--- a/data/mathtests/CDPresults.xlsx
+++ b/data/mathtests/CDPresults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\segmentation\data\mathtests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5852251F-1101-4B47-9D76-46A447844732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B19A6A-ABC2-4F77-9BA3-C75FC71FB814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="348" yWindow="792" windowWidth="18372" windowHeight="12888" activeTab="1" xr2:uid="{CBDF1A6D-5BCF-4736-9138-AFBBECA9C390}"/>
+    <workbookView xWindow="11430" yWindow="450" windowWidth="16665" windowHeight="14760" activeTab="1" xr2:uid="{CBDF1A6D-5BCF-4736-9138-AFBBECA9C390}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="106">
   <si>
     <t>M3</t>
   </si>
@@ -54,42 +52,6 @@
     <t>M4</t>
   </si>
   <si>
-    <t>ABBV</t>
-  </si>
-  <si>
-    <t>BTCUSD</t>
-  </si>
-  <si>
-    <t>EURCHF</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>EWG</t>
-  </si>
-  <si>
-    <t>EWQ</t>
-  </si>
-  <si>
-    <t>EWZ</t>
-  </si>
-  <si>
-    <t>PYPL</t>
-  </si>
-  <si>
-    <t>RBLX</t>
-  </si>
-  <si>
-    <t>ROST</t>
-  </si>
-  <si>
-    <t>SLV</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>M6</t>
   </si>
   <si>
@@ -309,9 +271,6 @@
     <t>n</t>
   </si>
   <si>
-    <t>EWX</t>
-  </si>
-  <si>
     <t>Demographic</t>
   </si>
   <si>
@@ -361,6 +320,42 @@
   </si>
   <si>
     <t>Benchmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ABBV</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> COP</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HST</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PYPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ROST</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EWG</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EWQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EWZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SLV</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VXX</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>ETF</t>
   </si>
 </sst>
 </file>
@@ -368,7 +363,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -419,7 +414,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -754,76 +749,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD3AE39-D579-4A59-9D7D-E59F3DFD4610}">
-  <dimension ref="A1:P145"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P143"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L1" t="s">
         <v>88</v>
       </c>
-      <c r="F1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L1" t="s">
-        <v>101</v>
-      </c>
       <c r="M1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="N1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="O1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="P1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E2">
         <v>134</v>
@@ -870,18 +865,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E3">
         <v>135</v>
@@ -897,18 +892,18 @@
       </c>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E4">
         <v>135</v>
@@ -924,18 +919,18 @@
       </c>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E5">
         <v>71</v>
@@ -951,18 +946,18 @@
       </c>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E6">
         <v>138</v>
@@ -978,18 +973,18 @@
       </c>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E7">
         <v>79</v>
@@ -1036,18 +1031,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E8">
         <v>133</v>
@@ -1063,18 +1058,18 @@
       </c>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E9">
         <v>134</v>
@@ -1090,18 +1085,18 @@
       </c>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E10">
         <v>134</v>
@@ -1117,18 +1112,18 @@
       </c>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E11">
         <v>144</v>
@@ -1144,18 +1139,18 @@
       </c>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E12">
         <v>140</v>
@@ -1202,18 +1197,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E13">
         <v>134</v>
@@ -1229,18 +1224,18 @@
       </c>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E14">
         <v>133</v>
@@ -1256,18 +1251,18 @@
       </c>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E15">
         <v>144</v>
@@ -1283,18 +1278,18 @@
       </c>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E16">
         <v>144</v>
@@ -1310,18 +1305,18 @@
       </c>
       <c r="I16" s="2"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E17">
         <v>120</v>
@@ -1368,18 +1363,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E18">
         <v>98</v>
@@ -1395,18 +1390,18 @@
       </c>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E19">
         <v>134</v>
@@ -1422,18 +1417,18 @@
       </c>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E20">
         <v>144</v>
@@ -1449,18 +1444,18 @@
       </c>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E21">
         <v>144</v>
@@ -1476,18 +1471,18 @@
       </c>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E22">
         <v>126</v>
@@ -1534,18 +1529,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E23">
         <v>69</v>
@@ -1561,18 +1556,18 @@
       </c>
       <c r="I23" s="2"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E24">
         <v>69</v>
@@ -1588,18 +1583,18 @@
       </c>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E25">
         <v>69</v>
@@ -1615,18 +1610,18 @@
       </c>
       <c r="I25" s="2"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E26">
         <v>126</v>
@@ -1642,18 +1637,18 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E27">
         <v>71</v>
@@ -1700,18 +1695,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E28">
         <v>71</v>
@@ -1727,18 +1722,18 @@
       </c>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E29">
         <v>71</v>
@@ -1754,18 +1749,18 @@
       </c>
       <c r="I29" s="2"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E30">
         <v>71</v>
@@ -1781,18 +1776,18 @@
       </c>
       <c r="I30" s="2"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E31">
         <v>120</v>
@@ -1808,18 +1803,18 @@
       </c>
       <c r="I31" s="2"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E32">
         <v>126</v>
@@ -1866,18 +1861,18 @@
         <v>288</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E33">
         <v>111</v>
@@ -1893,18 +1888,18 @@
       </c>
       <c r="I33" s="2"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E34">
         <v>115</v>
@@ -1920,18 +1915,18 @@
       </c>
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E35">
         <v>122</v>
@@ -1947,18 +1942,18 @@
       </c>
       <c r="I35" s="2"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E36">
         <v>735</v>
@@ -1974,18 +1969,18 @@
       </c>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E37">
         <v>136</v>
@@ -2032,18 +2027,18 @@
         <v>308</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D38" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E38">
         <v>116</v>
@@ -2059,18 +2054,18 @@
       </c>
       <c r="I38" s="2"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E39">
         <v>123</v>
@@ -2086,18 +2081,18 @@
       </c>
       <c r="I39" s="2"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E40">
         <v>117</v>
@@ -2113,7 +2108,7 @@
       </c>
       <c r="I40" s="2"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2121,10 +2116,10 @@
         <v>1</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E41">
         <v>738</v>
@@ -2140,18 +2135,18 @@
       </c>
       <c r="I41" s="2"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E42">
         <v>162</v>
@@ -2198,18 +2193,18 @@
         <v>298</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D43" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E43">
         <v>122</v>
@@ -2225,18 +2220,18 @@
       </c>
       <c r="I43" s="2"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D44" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E44">
         <v>118</v>
@@ -2252,18 +2247,18 @@
       </c>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D45" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E45">
         <v>153</v>
@@ -2279,18 +2274,18 @@
       </c>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E46">
         <v>737</v>
@@ -2306,18 +2301,18 @@
       </c>
       <c r="I46" s="2"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E47">
         <v>164</v>
@@ -2364,18 +2359,18 @@
         <v>532</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E48">
         <v>126</v>
@@ -2391,18 +2386,18 @@
       </c>
       <c r="I48" s="2"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E49">
         <v>118</v>
@@ -2418,18 +2413,18 @@
       </c>
       <c r="I49" s="2"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E50">
         <v>126</v>
@@ -2445,7 +2440,7 @@
       </c>
       <c r="I50" s="2"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2453,10 +2448,10 @@
         <v>2</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E51">
         <v>866</v>
@@ -2472,18 +2467,18 @@
       </c>
       <c r="I51" s="2"/>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D52" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E52">
         <v>109</v>
@@ -2530,18 +2525,18 @@
         <v>292</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E53">
         <v>106</v>
@@ -2557,18 +2552,18 @@
       </c>
       <c r="I53" s="2"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D54" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E54">
         <v>106</v>
@@ -2584,18 +2579,18 @@
       </c>
       <c r="I54" s="2"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D55" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E55">
         <v>106</v>
@@ -2611,18 +2606,18 @@
       </c>
       <c r="I55" s="2"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D56" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E56">
         <v>737</v>
@@ -2638,18 +2633,18 @@
       </c>
       <c r="I56" s="2"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D57" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E57">
         <v>180</v>
@@ -2696,18 +2691,18 @@
         <v>286</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D58" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E58">
         <v>177</v>
@@ -2723,18 +2718,18 @@
       </c>
       <c r="I58" s="2"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D59" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E59">
         <v>122</v>
@@ -2750,18 +2745,18 @@
       </c>
       <c r="I59" s="2"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D60" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E60">
         <v>122</v>
@@ -2777,18 +2772,18 @@
       </c>
       <c r="I60" s="2"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D61" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E61">
         <v>701</v>
@@ -2804,19 +2799,19 @@
       </c>
       <c r="I61" s="2"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62">
         <f>1+A61</f>
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>4</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>19</v>
+        <v>94</v>
+      </c>
+      <c r="C62" t="s">
+        <v>104</v>
       </c>
       <c r="D62" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E62">
         <v>253</v>
@@ -2831,107 +2826,107 @@
         <v>5</v>
       </c>
       <c r="I62" s="2">
-        <f>AVERAGE(E62:E73)</f>
+        <f>AVERAGE(E62:E71)</f>
+        <v>257.8</v>
+      </c>
+      <c r="J62">
+        <f>MAX(E62:E71)</f>
         <v>265</v>
       </c>
-      <c r="J62">
-        <f>MAX(E62:E73)</f>
-        <v>367</v>
-      </c>
       <c r="K62" s="2">
-        <f>AVERAGE(F62:F73)</f>
-        <v>32627.083333333332</v>
+        <f>AVERAGE(F62:F71)</f>
+        <v>30394.2</v>
       </c>
       <c r="L62">
-        <f>MAX(F62:F73)</f>
-        <v>61423</v>
+        <f>MAX(F62:F71)</f>
+        <v>32131</v>
       </c>
       <c r="M62" s="2">
-        <f>AVERAGE(G62:G73)</f>
-        <v>3.0833333333333335</v>
+        <f>AVERAGE(G62:G71)</f>
+        <v>4.2</v>
       </c>
       <c r="N62">
-        <f>MAX(G62:G73)</f>
+        <f>MAX(G62:G71)</f>
         <v>7</v>
       </c>
       <c r="O62" s="2">
-        <f>AVERAGE(H62:H73)</f>
-        <v>7.583333333333333</v>
+        <f>AVERAGE(H62:H71)</f>
+        <v>7</v>
       </c>
       <c r="P62">
-        <f>MAX(H62:H73)</f>
+        <f>MAX(H62:H71)</f>
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63">
-        <f t="shared" ref="A63:A73" si="0">1+A62</f>
+        <f t="shared" ref="A63:A71" si="0">1+A62</f>
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
+      </c>
+      <c r="C63" t="s">
+        <v>104</v>
       </c>
       <c r="D63" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E63">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="F63">
-        <v>29403</v>
+        <v>32131</v>
       </c>
       <c r="G63">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H63">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I63" s="2"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>19</v>
+        <v>96</v>
+      </c>
+      <c r="C64" t="s">
+        <v>104</v>
       </c>
       <c r="D64" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E64">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="F64">
-        <v>29403</v>
+        <v>32131</v>
       </c>
       <c r="G64">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H64">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I64" s="2"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>89</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>19</v>
+        <v>97</v>
+      </c>
+      <c r="C65" t="s">
+        <v>104</v>
       </c>
       <c r="D65" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E65">
         <v>253</v>
@@ -2947,19 +2942,19 @@
       </c>
       <c r="I65" s="2"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>19</v>
+        <v>98</v>
+      </c>
+      <c r="C66" t="s">
+        <v>104</v>
       </c>
       <c r="D66" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E66">
         <v>253</v>
@@ -2975,19 +2970,19 @@
       </c>
       <c r="I66" s="2"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>19</v>
+        <v>99</v>
+      </c>
+      <c r="C67" t="s">
+        <v>105</v>
       </c>
       <c r="D67" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E67">
         <v>253</v>
@@ -3003,19 +2998,19 @@
       </c>
       <c r="I67" s="2"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>19</v>
+        <v>100</v>
+      </c>
+      <c r="C68" t="s">
+        <v>105</v>
       </c>
       <c r="D68" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E68">
         <v>253</v>
@@ -3031,19 +3026,19 @@
       </c>
       <c r="I68" s="2"/>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>14</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>19</v>
+        <v>101</v>
+      </c>
+      <c r="C69" t="s">
+        <v>105</v>
       </c>
       <c r="D69" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E69">
         <v>253</v>
@@ -3059,25 +3054,25 @@
       </c>
       <c r="I69" s="2"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>5</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>19</v>
+        <v>102</v>
+      </c>
+      <c r="C70" t="s">
+        <v>105</v>
       </c>
       <c r="D70" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E70">
-        <v>367</v>
+        <v>265</v>
       </c>
       <c r="F70">
-        <v>61423</v>
+        <v>32131</v>
       </c>
       <c r="G70">
         <v>2</v>
@@ -3087,25 +3082,25 @@
       </c>
       <c r="I70" s="2"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>19</v>
+        <v>103</v>
+      </c>
+      <c r="C71" t="s">
+        <v>105</v>
       </c>
       <c r="D71" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E71">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F71">
-        <v>31626</v>
+        <v>31131</v>
       </c>
       <c r="G71">
         <v>3</v>
@@ -3115,796 +3110,794 @@
       </c>
       <c r="I71" s="2"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72">
-        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D72" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72">
+        <v>134</v>
+      </c>
+      <c r="F72">
+        <v>8128</v>
+      </c>
+      <c r="G72">
+        <v>10</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2">
+        <f>AVERAGE(E72:E76)</f>
+        <v>122.6</v>
+      </c>
+      <c r="J72">
+        <f>MAX(E72:E76)</f>
+        <v>138</v>
+      </c>
+      <c r="K72" s="2">
+        <f>AVERAGE(F72:F76)</f>
+        <v>7073.2</v>
+      </c>
+      <c r="L72">
+        <f>MAX(F72:F76)</f>
+        <v>8646</v>
+      </c>
+      <c r="M72" s="2">
+        <f>AVERAGE(G72:G76)</f>
+        <v>9.4</v>
+      </c>
+      <c r="N72">
+        <f>MAX(G72:G76)</f>
+        <v>10</v>
+      </c>
+      <c r="O72" s="2">
+        <f>AVERAGE(H72:H76)</f>
+        <v>0.2</v>
+      </c>
+      <c r="P72">
+        <f>MAX(H72:H76)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2</v>
+      </c>
+      <c r="B73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73">
+        <v>135</v>
+      </c>
+      <c r="F73">
+        <v>8256</v>
+      </c>
+      <c r="G73">
+        <v>10</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73" s="2"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>3</v>
+      </c>
+      <c r="B74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74">
+        <v>135</v>
+      </c>
+      <c r="F74">
+        <v>8256</v>
+      </c>
+      <c r="G74">
+        <v>10</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>4</v>
+      </c>
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D75" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
+      <c r="F75">
+        <v>2080</v>
+      </c>
+      <c r="G75">
         <v>7</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75" s="2"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>5</v>
+      </c>
+      <c r="B76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76">
+        <v>138</v>
+      </c>
+      <c r="F76">
+        <v>8646</v>
+      </c>
+      <c r="G76">
+        <v>10</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76" s="2"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>6</v>
+      </c>
+      <c r="B77" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77">
+        <v>79</v>
+      </c>
+      <c r="F77">
+        <v>2628</v>
+      </c>
+      <c r="G77">
+        <v>8</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77" s="2">
+        <f>AVERAGE(E77:E81)</f>
+        <v>124.8</v>
+      </c>
+      <c r="J77">
+        <f>MAX(E77:E81)</f>
+        <v>144</v>
+      </c>
+      <c r="K77" s="2">
+        <f>AVERAGE(F77:F81)</f>
+        <v>7267.6</v>
+      </c>
+      <c r="L77">
+        <f>MAX(F77:F81)</f>
+        <v>9453</v>
+      </c>
+      <c r="M77" s="2">
+        <f>AVERAGE(G77:G81)</f>
+        <v>9.6</v>
+      </c>
+      <c r="N77">
+        <f>MAX(G77:G81)</f>
+        <v>10</v>
+      </c>
+      <c r="O77" s="2">
+        <f>AVERAGE(H77:H81)</f>
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <f>MAX(H77:H81)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>7</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78">
+        <v>133</v>
+      </c>
+      <c r="F78">
+        <v>8001</v>
+      </c>
+      <c r="G78">
+        <v>10</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>8</v>
+      </c>
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79">
+        <v>134</v>
+      </c>
+      <c r="F79">
+        <v>8128</v>
+      </c>
+      <c r="G79">
+        <v>10</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79" s="2"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>9</v>
+      </c>
+      <c r="B80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80">
+        <v>134</v>
+      </c>
+      <c r="F80">
+        <v>8128</v>
+      </c>
+      <c r="G80">
+        <v>10</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80" s="2"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>10</v>
+      </c>
+      <c r="B81" t="s">
         <v>19</v>
       </c>
-      <c r="D72" t="s">
+      <c r="C81" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E72">
-        <v>263</v>
-      </c>
-      <c r="F72">
-        <v>31626</v>
-      </c>
-      <c r="G72">
-        <v>1</v>
-      </c>
-      <c r="H72">
-        <v>7</v>
-      </c>
-      <c r="I72" s="2"/>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <f t="shared" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81">
+        <v>144</v>
+      </c>
+      <c r="F81">
+        <v>9453</v>
+      </c>
+      <c r="G81">
+        <v>10</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81" s="2"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>11</v>
+      </c>
+      <c r="B82" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82">
+        <v>140</v>
+      </c>
+      <c r="F82">
+        <v>8911</v>
+      </c>
+      <c r="G82">
+        <v>10</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82" s="2">
+        <f>AVERAGE(E82:E86)</f>
+        <v>139</v>
+      </c>
+      <c r="J82">
+        <f>MAX(E82:E86)</f>
+        <v>144</v>
+      </c>
+      <c r="K82" s="2">
+        <f>AVERAGE(F82:F86)</f>
+        <v>8789.2000000000007</v>
+      </c>
+      <c r="L82">
+        <f>MAX(F82:F86)</f>
+        <v>9453</v>
+      </c>
+      <c r="M82" s="2">
+        <f>AVERAGE(G82:G86)</f>
+        <v>10</v>
+      </c>
+      <c r="N82">
+        <f>MAX(G82:G86)</f>
+        <v>10</v>
+      </c>
+      <c r="O82" s="2">
+        <f>AVERAGE(H82:H86)</f>
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <f>MAX(H82:H86)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>12</v>
+      </c>
+      <c r="B83" t="s">
+        <v>21</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D83" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83">
+        <v>134</v>
+      </c>
+      <c r="F83">
+        <v>8128</v>
+      </c>
+      <c r="G83">
+        <v>10</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83" s="2"/>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>13</v>
+      </c>
+      <c r="B84" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84">
+        <v>133</v>
+      </c>
+      <c r="F84">
+        <v>8001</v>
+      </c>
+      <c r="G84">
+        <v>10</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84" s="2"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>14</v>
+      </c>
+      <c r="B85" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D85" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85">
+        <v>144</v>
+      </c>
+      <c r="F85">
+        <v>9453</v>
+      </c>
+      <c r="G85">
+        <v>10</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85" s="2"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86">
         <v>15</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="B86" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D86" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86">
+        <v>144</v>
+      </c>
+      <c r="F86">
+        <v>9453</v>
+      </c>
+      <c r="G86">
+        <v>10</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86" s="2"/>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>16</v>
+      </c>
+      <c r="B87" t="s">
+        <v>25</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D87" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87">
+        <v>120</v>
+      </c>
+      <c r="F87">
+        <v>6441</v>
+      </c>
+      <c r="G87">
+        <v>10</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87" s="2">
+        <f>AVERAGE(E87:E91)</f>
+        <v>128</v>
+      </c>
+      <c r="J87">
+        <f>MAX(E87:E91)</f>
+        <v>144</v>
+      </c>
+      <c r="K87" s="2">
+        <f>AVERAGE(F87:F91)</f>
+        <v>7532.2</v>
+      </c>
+      <c r="L87">
+        <f>MAX(F87:F91)</f>
+        <v>9453</v>
+      </c>
+      <c r="M87" s="2">
+        <f>AVERAGE(G87:G91)</f>
+        <v>10</v>
+      </c>
+      <c r="N87">
+        <f>MAX(G87:G91)</f>
+        <v>10</v>
+      </c>
+      <c r="O87" s="2">
+        <f>AVERAGE(H87:H91)</f>
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <f>MAX(H87:H91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>17</v>
+      </c>
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D88" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88">
+        <v>98</v>
+      </c>
+      <c r="F88">
+        <v>4186</v>
+      </c>
+      <c r="G88">
+        <v>10</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88" s="2"/>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>18</v>
+      </c>
+      <c r="B89" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89">
+        <v>134</v>
+      </c>
+      <c r="F89">
+        <v>8128</v>
+      </c>
+      <c r="G89">
+        <v>10</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89" s="2"/>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90">
         <v>19</v>
       </c>
-      <c r="D73" t="s">
-        <v>80</v>
-      </c>
-      <c r="E73">
-        <v>263</v>
-      </c>
-      <c r="F73">
-        <v>31626</v>
-      </c>
-      <c r="G73">
-        <v>1</v>
-      </c>
-      <c r="H73">
-        <v>6</v>
-      </c>
-      <c r="I73" s="2"/>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>1</v>
-      </c>
-      <c r="B74" t="s">
+      <c r="B90" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D90" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90">
+        <v>144</v>
+      </c>
+      <c r="F90">
+        <v>9453</v>
+      </c>
+      <c r="G90">
+        <v>10</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90" s="2"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>20</v>
+      </c>
+      <c r="B91" t="s">
+        <v>29</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D91" t="s">
+        <v>69</v>
+      </c>
+      <c r="E91">
+        <v>144</v>
+      </c>
+      <c r="F91">
+        <v>9453</v>
+      </c>
+      <c r="G91">
+        <v>10</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91" s="2"/>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>21</v>
+      </c>
+      <c r="B92" t="s">
+        <v>30</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92">
+        <v>126</v>
+      </c>
+      <c r="F92">
+        <v>7140</v>
+      </c>
+      <c r="G92">
+        <v>10</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92" s="2">
+        <f>AVERAGE(E92:E96)</f>
+        <v>91.8</v>
+      </c>
+      <c r="J92">
+        <f>MAX(E92:E96)</f>
+        <v>126</v>
+      </c>
+      <c r="K92" s="2">
+        <f>AVERAGE(F92:F96)</f>
+        <v>4027.8</v>
+      </c>
+      <c r="L92">
+        <f>MAX(F92:F96)</f>
+        <v>7140</v>
+      </c>
+      <c r="M92" s="2">
+        <f>AVERAGE(G92:G96)</f>
+        <v>6.6</v>
+      </c>
+      <c r="N92">
+        <f>MAX(G92:G96)</f>
+        <v>10</v>
+      </c>
+      <c r="O92" s="2">
+        <f>AVERAGE(H92:H96)</f>
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <f>MAX(H92:H96)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>22</v>
+      </c>
+      <c r="B93" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93">
+        <v>69</v>
+      </c>
+      <c r="F93">
+        <v>1953</v>
+      </c>
+      <c r="G93">
+        <v>5</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93" s="2"/>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94">
         <v>23</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D74" t="s">
-        <v>81</v>
-      </c>
-      <c r="E74">
-        <v>134</v>
-      </c>
-      <c r="F74">
-        <v>8128</v>
-      </c>
-      <c r="G74">
-        <v>10</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74" s="2">
-        <f>AVERAGE(E74:E78)</f>
-        <v>122.6</v>
-      </c>
-      <c r="J74">
-        <f>MAX(E74:E78)</f>
-        <v>138</v>
-      </c>
-      <c r="K74" s="2">
-        <f>AVERAGE(F74:F78)</f>
-        <v>7073.2</v>
-      </c>
-      <c r="L74">
-        <f>MAX(F74:F78)</f>
-        <v>8646</v>
-      </c>
-      <c r="M74" s="2">
-        <f>AVERAGE(G74:G78)</f>
-        <v>9.4</v>
-      </c>
-      <c r="N74">
-        <f>MAX(G74:G78)</f>
-        <v>10</v>
-      </c>
-      <c r="O74" s="2">
-        <f>AVERAGE(H74:H78)</f>
-        <v>0.2</v>
-      </c>
-      <c r="P74">
-        <f>MAX(H74:H78)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>2</v>
-      </c>
-      <c r="B75" t="s">
+      <c r="B94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94">
+        <v>69</v>
+      </c>
+      <c r="F94">
+        <v>1953</v>
+      </c>
+      <c r="G94">
+        <v>4</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94" s="2"/>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95">
         <v>24</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D75" t="s">
-        <v>81</v>
-      </c>
-      <c r="E75">
-        <v>135</v>
-      </c>
-      <c r="F75">
-        <v>8256</v>
-      </c>
-      <c r="G75">
-        <v>10</v>
-      </c>
-      <c r="H75">
-        <v>1</v>
-      </c>
-      <c r="I75" s="2"/>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <v>3</v>
-      </c>
-      <c r="B76" t="s">
-        <v>25</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D76" t="s">
-        <v>81</v>
-      </c>
-      <c r="E76">
-        <v>135</v>
-      </c>
-      <c r="F76">
-        <v>8256</v>
-      </c>
-      <c r="G76">
-        <v>10</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76" s="2"/>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>4</v>
-      </c>
-      <c r="B77" t="s">
-        <v>22</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D77" t="s">
-        <v>81</v>
-      </c>
-      <c r="E77">
-        <v>71</v>
-      </c>
-      <c r="F77">
-        <v>2080</v>
-      </c>
-      <c r="G77">
-        <v>7</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77" s="2"/>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>5</v>
-      </c>
-      <c r="B78" t="s">
-        <v>26</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D78" t="s">
-        <v>81</v>
-      </c>
-      <c r="E78">
-        <v>138</v>
-      </c>
-      <c r="F78">
-        <v>8646</v>
-      </c>
-      <c r="G78">
-        <v>10</v>
-      </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
-      <c r="I78" s="2"/>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>6</v>
-      </c>
-      <c r="B79" t="s">
-        <v>27</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D79" t="s">
-        <v>81</v>
-      </c>
-      <c r="E79">
-        <v>79</v>
-      </c>
-      <c r="F79">
-        <v>2628</v>
-      </c>
-      <c r="G79">
-        <v>8</v>
-      </c>
-      <c r="H79">
-        <v>0</v>
-      </c>
-      <c r="I79" s="2">
-        <f>AVERAGE(E79:E83)</f>
-        <v>124.8</v>
-      </c>
-      <c r="J79">
-        <f>MAX(E79:E83)</f>
-        <v>144</v>
-      </c>
-      <c r="K79" s="2">
-        <f>AVERAGE(F79:F83)</f>
-        <v>7267.6</v>
-      </c>
-      <c r="L79">
-        <f>MAX(F79:F83)</f>
-        <v>9453</v>
-      </c>
-      <c r="M79" s="2">
-        <f>AVERAGE(G79:G83)</f>
-        <v>9.6</v>
-      </c>
-      <c r="N79">
-        <f>MAX(G79:G83)</f>
-        <v>10</v>
-      </c>
-      <c r="O79" s="2">
-        <f>AVERAGE(H79:H83)</f>
-        <v>0</v>
-      </c>
-      <c r="P79">
-        <f>MAX(H79:H83)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>7</v>
-      </c>
-      <c r="B80" t="s">
-        <v>28</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D80" t="s">
-        <v>81</v>
-      </c>
-      <c r="E80">
-        <v>133</v>
-      </c>
-      <c r="F80">
-        <v>8001</v>
-      </c>
-      <c r="G80">
-        <v>10</v>
-      </c>
-      <c r="H80">
-        <v>0</v>
-      </c>
-      <c r="I80" s="2"/>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A81">
-        <v>8</v>
-      </c>
-      <c r="B81" t="s">
-        <v>29</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D81" t="s">
-        <v>81</v>
-      </c>
-      <c r="E81">
-        <v>134</v>
-      </c>
-      <c r="F81">
-        <v>8128</v>
-      </c>
-      <c r="G81">
-        <v>10</v>
-      </c>
-      <c r="H81">
-        <v>0</v>
-      </c>
-      <c r="I81" s="2"/>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A82">
-        <v>9</v>
-      </c>
-      <c r="B82" t="s">
-        <v>30</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D82" t="s">
-        <v>81</v>
-      </c>
-      <c r="E82">
-        <v>134</v>
-      </c>
-      <c r="F82">
-        <v>8128</v>
-      </c>
-      <c r="G82">
-        <v>10</v>
-      </c>
-      <c r="H82">
-        <v>0</v>
-      </c>
-      <c r="I82" s="2"/>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A83">
-        <v>10</v>
-      </c>
-      <c r="B83" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D83" t="s">
-        <v>81</v>
-      </c>
-      <c r="E83">
-        <v>144</v>
-      </c>
-      <c r="F83">
-        <v>9453</v>
-      </c>
-      <c r="G83">
-        <v>10</v>
-      </c>
-      <c r="H83">
-        <v>0</v>
-      </c>
-      <c r="I83" s="2"/>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A84">
-        <v>11</v>
-      </c>
-      <c r="B84" t="s">
-        <v>32</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D84" t="s">
-        <v>81</v>
-      </c>
-      <c r="E84">
-        <v>140</v>
-      </c>
-      <c r="F84">
-        <v>8911</v>
-      </c>
-      <c r="G84">
-        <v>10</v>
-      </c>
-      <c r="H84">
-        <v>0</v>
-      </c>
-      <c r="I84" s="2">
-        <f>AVERAGE(E84:E88)</f>
-        <v>139</v>
-      </c>
-      <c r="J84">
-        <f>MAX(E84:E88)</f>
-        <v>144</v>
-      </c>
-      <c r="K84" s="2">
-        <f>AVERAGE(F84:F88)</f>
-        <v>8789.2000000000007</v>
-      </c>
-      <c r="L84">
-        <f>MAX(F84:F88)</f>
-        <v>9453</v>
-      </c>
-      <c r="M84" s="2">
-        <f>AVERAGE(G84:G88)</f>
-        <v>10</v>
-      </c>
-      <c r="N84">
-        <f>MAX(G84:G88)</f>
-        <v>10</v>
-      </c>
-      <c r="O84" s="2">
-        <f>AVERAGE(H84:H88)</f>
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <f>MAX(H84:H88)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A85">
-        <v>12</v>
-      </c>
-      <c r="B85" t="s">
+      <c r="B95" t="s">
         <v>33</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D85" t="s">
-        <v>81</v>
-      </c>
-      <c r="E85">
-        <v>134</v>
-      </c>
-      <c r="F85">
-        <v>8128</v>
-      </c>
-      <c r="G85">
-        <v>10</v>
-      </c>
-      <c r="H85">
-        <v>0</v>
-      </c>
-      <c r="I85" s="2"/>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A86">
-        <v>13</v>
-      </c>
-      <c r="B86" t="s">
-        <v>34</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D86" t="s">
-        <v>81</v>
-      </c>
-      <c r="E86">
-        <v>133</v>
-      </c>
-      <c r="F86">
-        <v>8001</v>
-      </c>
-      <c r="G86">
-        <v>10</v>
-      </c>
-      <c r="H86">
-        <v>0</v>
-      </c>
-      <c r="I86" s="2"/>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <v>14</v>
-      </c>
-      <c r="B87" t="s">
-        <v>35</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D87" t="s">
-        <v>81</v>
-      </c>
-      <c r="E87">
-        <v>144</v>
-      </c>
-      <c r="F87">
-        <v>9453</v>
-      </c>
-      <c r="G87">
-        <v>10</v>
-      </c>
-      <c r="H87">
-        <v>0</v>
-      </c>
-      <c r="I87" s="2"/>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>36</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D88" t="s">
-        <v>81</v>
-      </c>
-      <c r="E88">
-        <v>144</v>
-      </c>
-      <c r="F88">
-        <v>9453</v>
-      </c>
-      <c r="G88">
-        <v>10</v>
-      </c>
-      <c r="H88">
-        <v>0</v>
-      </c>
-      <c r="I88" s="2"/>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>16</v>
-      </c>
-      <c r="B89" t="s">
-        <v>37</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D89" t="s">
-        <v>81</v>
-      </c>
-      <c r="E89">
-        <v>120</v>
-      </c>
-      <c r="F89">
-        <v>6441</v>
-      </c>
-      <c r="G89">
-        <v>10</v>
-      </c>
-      <c r="H89">
-        <v>0</v>
-      </c>
-      <c r="I89" s="2">
-        <f>AVERAGE(E89:E93)</f>
-        <v>128</v>
-      </c>
-      <c r="J89">
-        <f>MAX(E89:E93)</f>
-        <v>144</v>
-      </c>
-      <c r="K89" s="2">
-        <f>AVERAGE(F89:F93)</f>
-        <v>7532.2</v>
-      </c>
-      <c r="L89">
-        <f>MAX(F89:F93)</f>
-        <v>9453</v>
-      </c>
-      <c r="M89" s="2">
-        <f>AVERAGE(G89:G93)</f>
-        <v>10</v>
-      </c>
-      <c r="N89">
-        <f>MAX(G89:G93)</f>
-        <v>10</v>
-      </c>
-      <c r="O89" s="2">
-        <f>AVERAGE(H89:H93)</f>
-        <v>0</v>
-      </c>
-      <c r="P89">
-        <f>MAX(H89:H93)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>17</v>
-      </c>
-      <c r="B90" t="s">
-        <v>38</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D90" t="s">
-        <v>81</v>
-      </c>
-      <c r="E90">
-        <v>98</v>
-      </c>
-      <c r="F90">
-        <v>4186</v>
-      </c>
-      <c r="G90">
-        <v>10</v>
-      </c>
-      <c r="H90">
-        <v>0</v>
-      </c>
-      <c r="I90" s="2"/>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>18</v>
-      </c>
-      <c r="B91" t="s">
-        <v>39</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D91" t="s">
-        <v>81</v>
-      </c>
-      <c r="E91">
-        <v>134</v>
-      </c>
-      <c r="F91">
-        <v>8128</v>
-      </c>
-      <c r="G91">
-        <v>10</v>
-      </c>
-      <c r="H91">
-        <v>0</v>
-      </c>
-      <c r="I91" s="2"/>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <v>19</v>
-      </c>
-      <c r="B92" t="s">
-        <v>40</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D92" t="s">
-        <v>81</v>
-      </c>
-      <c r="E92">
-        <v>144</v>
-      </c>
-      <c r="F92">
-        <v>9453</v>
-      </c>
-      <c r="G92">
-        <v>10</v>
-      </c>
-      <c r="H92">
-        <v>0</v>
-      </c>
-      <c r="I92" s="2"/>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <v>20</v>
-      </c>
-      <c r="B93" t="s">
-        <v>41</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D93" t="s">
-        <v>81</v>
-      </c>
-      <c r="E93">
-        <v>144</v>
-      </c>
-      <c r="F93">
-        <v>9453</v>
-      </c>
-      <c r="G93">
-        <v>10</v>
-      </c>
-      <c r="H93">
-        <v>0</v>
-      </c>
-      <c r="I93" s="2"/>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A94">
-        <v>21</v>
-      </c>
-      <c r="B94" t="s">
-        <v>42</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D94" t="s">
-        <v>81</v>
-      </c>
-      <c r="E94">
-        <v>126</v>
-      </c>
-      <c r="F94">
-        <v>7140</v>
-      </c>
-      <c r="G94">
-        <v>10</v>
-      </c>
-      <c r="H94">
-        <v>0</v>
-      </c>
-      <c r="I94" s="2">
-        <f>AVERAGE(E94:E98)</f>
-        <v>91.8</v>
-      </c>
-      <c r="J94">
-        <f>MAX(E94:E98)</f>
-        <v>126</v>
-      </c>
-      <c r="K94" s="2">
-        <f>AVERAGE(F94:F98)</f>
-        <v>4027.8</v>
-      </c>
-      <c r="L94">
-        <f>MAX(F94:F98)</f>
-        <v>7140</v>
-      </c>
-      <c r="M94" s="2">
-        <f>AVERAGE(G94:G98)</f>
-        <v>6.6</v>
-      </c>
-      <c r="N94">
-        <f>MAX(G94:G98)</f>
-        <v>10</v>
-      </c>
-      <c r="O94" s="2">
-        <f>AVERAGE(H94:H98)</f>
-        <v>0</v>
-      </c>
-      <c r="P94">
-        <f>MAX(H94:H98)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <v>22</v>
-      </c>
-      <c r="B95" t="s">
-        <v>43</v>
-      </c>
       <c r="C95" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D95" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E95">
         <v>69</v>
@@ -3913,106 +3906,137 @@
         <v>1953</v>
       </c>
       <c r="G95">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H95">
         <v>0</v>
       </c>
       <c r="I95" s="2"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D96" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E96">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="F96">
-        <v>1953</v>
+        <v>7140</v>
       </c>
       <c r="G96">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H96">
         <v>0</v>
       </c>
       <c r="I96" s="2"/>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B97" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D97" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E97">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F97">
-        <v>1953</v>
+        <v>2080</v>
       </c>
       <c r="G97">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H97">
         <v>0</v>
       </c>
-      <c r="I97" s="2"/>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I97" s="2">
+        <f>AVERAGE(E97:E101)</f>
+        <v>80.8</v>
+      </c>
+      <c r="J97">
+        <f>MAX(E97:E101)</f>
+        <v>120</v>
+      </c>
+      <c r="K97" s="2">
+        <f>AVERAGE(F97:F101)</f>
+        <v>2952.2</v>
+      </c>
+      <c r="L97">
+        <f>MAX(F97:F101)</f>
+        <v>6441</v>
+      </c>
+      <c r="M97" s="2">
+        <f>AVERAGE(G97:G101)</f>
+        <v>7.4</v>
+      </c>
+      <c r="N97">
+        <f>MAX(G97:G101)</f>
+        <v>9</v>
+      </c>
+      <c r="O97" s="2">
+        <f>AVERAGE(H97:H101)</f>
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <f>MAX(H97:H101)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D98" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E98">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="F98">
-        <v>7140</v>
+        <v>2080</v>
       </c>
       <c r="G98">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H98">
         <v>0</v>
       </c>
       <c r="I98" s="2"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B99" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D99" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E99">
         <v>71</v>
@@ -4026,51 +4050,20 @@
       <c r="H99">
         <v>0</v>
       </c>
-      <c r="I99" s="2">
-        <f>AVERAGE(E99:E103)</f>
-        <v>80.8</v>
-      </c>
-      <c r="J99">
-        <f>MAX(E99:E103)</f>
-        <v>120</v>
-      </c>
-      <c r="K99" s="2">
-        <f>AVERAGE(F99:F103)</f>
-        <v>2952.2</v>
-      </c>
-      <c r="L99">
-        <f>MAX(F99:F103)</f>
-        <v>6441</v>
-      </c>
-      <c r="M99" s="2">
-        <f>AVERAGE(G99:G103)</f>
-        <v>7.4</v>
-      </c>
-      <c r="N99">
-        <f>MAX(G99:G103)</f>
-        <v>9</v>
-      </c>
-      <c r="O99" s="2">
-        <f>AVERAGE(H99:H103)</f>
-        <v>0</v>
-      </c>
-      <c r="P99">
-        <f>MAX(H99:H103)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I99" s="2"/>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B100" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D100" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E100">
         <v>71</v>
@@ -4086,549 +4079,549 @@
       </c>
       <c r="I100" s="2"/>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B101" t="s">
+        <v>39</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101">
+        <v>120</v>
+      </c>
+      <c r="F101">
+        <v>6441</v>
+      </c>
+      <c r="G101">
+        <v>9</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101" s="2"/>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>31</v>
+      </c>
+      <c r="B102" t="s">
+        <v>40</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102">
+        <v>126</v>
+      </c>
+      <c r="F102">
+        <v>7140</v>
+      </c>
+      <c r="G102">
+        <v>10</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2">
+        <f>AVERAGE(E102:E106)</f>
+        <v>241.8</v>
+      </c>
+      <c r="J102">
+        <f>MAX(E102:E106)</f>
+        <v>735</v>
+      </c>
+      <c r="K102" s="2">
+        <f>AVERAGE(F102:F106)</f>
+        <v>54101.2</v>
+      </c>
+      <c r="L102">
+        <f>MAX(F102:F106)</f>
+        <v>245350</v>
+      </c>
+      <c r="M102" s="2">
+        <f>AVERAGE(G102:G106)</f>
+        <v>10</v>
+      </c>
+      <c r="N102">
+        <f>MAX(G102:G106)</f>
+        <v>10</v>
+      </c>
+      <c r="O102" s="2">
+        <f>AVERAGE(H102:H106)</f>
+        <v>58.4</v>
+      </c>
+      <c r="P102">
+        <f>MAX(H102:H106)</f>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>32</v>
+      </c>
+      <c r="B103" t="s">
+        <v>41</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103">
+        <v>111</v>
+      </c>
+      <c r="F103">
+        <v>5460</v>
+      </c>
+      <c r="G103">
+        <v>10</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103" s="2"/>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>33</v>
+      </c>
+      <c r="B104" t="s">
+        <v>42</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104">
+        <v>115</v>
+      </c>
+      <c r="F104">
+        <v>5886</v>
+      </c>
+      <c r="G104">
+        <v>10</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104" s="2"/>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>34</v>
+      </c>
+      <c r="B105" t="s">
+        <v>43</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105">
+        <v>122</v>
+      </c>
+      <c r="F105">
+        <v>6670</v>
+      </c>
+      <c r="G105">
+        <v>10</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105" s="2"/>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>35</v>
+      </c>
+      <c r="B106" t="s">
+        <v>44</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106">
+        <v>735</v>
+      </c>
+      <c r="F106">
+        <v>245350</v>
+      </c>
+      <c r="G106">
+        <v>10</v>
+      </c>
+      <c r="H106">
+        <v>292</v>
+      </c>
+      <c r="I106" s="2"/>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>36</v>
+      </c>
+      <c r="B107" t="s">
+        <v>45</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107">
+        <v>136</v>
+      </c>
+      <c r="F107">
+        <v>8385</v>
+      </c>
+      <c r="G107">
+        <v>10</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107" s="2">
+        <f>AVERAGE(E107:E111)</f>
+        <v>246</v>
+      </c>
+      <c r="J107">
+        <f>MAX(E107:E111)</f>
+        <v>738</v>
+      </c>
+      <c r="K107" s="2">
+        <f>AVERAGE(F107:F111)</f>
+        <v>54945.4</v>
+      </c>
+      <c r="L107">
+        <f>MAX(F107:F111)</f>
+        <v>247456</v>
+      </c>
+      <c r="M107" s="2">
+        <f>AVERAGE(G107:G111)</f>
+        <v>10</v>
+      </c>
+      <c r="N107">
+        <f>MAX(G107:G111)</f>
+        <v>10</v>
+      </c>
+      <c r="O107" s="2">
+        <f>AVERAGE(H107:H111)</f>
+        <v>65.2</v>
+      </c>
+      <c r="P107">
+        <f>MAX(H107:H111)</f>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>37</v>
+      </c>
+      <c r="B108" t="s">
+        <v>46</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108">
+        <v>116</v>
+      </c>
+      <c r="F108">
+        <v>5995</v>
+      </c>
+      <c r="G108">
+        <v>10</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108" s="2"/>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>38</v>
+      </c>
+      <c r="B109" t="s">
+        <v>47</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109">
+        <v>123</v>
+      </c>
+      <c r="F109">
+        <v>6786</v>
+      </c>
+      <c r="G109">
+        <v>10</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109" s="2"/>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>39</v>
+      </c>
+      <c r="B110" t="s">
+        <v>48</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110">
+        <v>117</v>
+      </c>
+      <c r="F110">
+        <v>6105</v>
+      </c>
+      <c r="G110">
+        <v>10</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110" s="2"/>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>40</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111">
+        <v>738</v>
+      </c>
+      <c r="F111">
+        <v>247456</v>
+      </c>
+      <c r="G111">
+        <v>10</v>
+      </c>
+      <c r="H111">
+        <v>325</v>
+      </c>
+      <c r="I111" s="2"/>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>41</v>
+      </c>
+      <c r="B112" t="s">
         <v>49</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D101" t="s">
-        <v>81</v>
-      </c>
-      <c r="E101">
-        <v>71</v>
-      </c>
-      <c r="F101">
-        <v>2080</v>
-      </c>
-      <c r="G101">
-        <v>7</v>
-      </c>
-      <c r="H101">
-        <v>0</v>
-      </c>
-      <c r="I101" s="2"/>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <v>29</v>
-      </c>
-      <c r="B102" t="s">
+      <c r="C112" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112">
+        <v>162</v>
+      </c>
+      <c r="F112">
+        <v>12090</v>
+      </c>
+      <c r="G112">
+        <v>10</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112" s="2">
+        <f>AVERAGE(E112:E116)</f>
+        <v>258.39999999999998</v>
+      </c>
+      <c r="J112">
+        <f>MAX(E112:E116)</f>
+        <v>737</v>
+      </c>
+      <c r="K112" s="2">
+        <f>AVERAGE(F112:F116)</f>
+        <v>56492</v>
+      </c>
+      <c r="L112">
+        <f>MAX(F112:F116)</f>
+        <v>246753</v>
+      </c>
+      <c r="M112" s="2">
+        <f>AVERAGE(G112:G116)</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N112">
+        <f>MAX(G112:G116)</f>
+        <v>10</v>
+      </c>
+      <c r="O112" s="2">
+        <f>AVERAGE(H112:H116)</f>
+        <v>62.4</v>
+      </c>
+      <c r="P112">
+        <f>MAX(H112:H116)</f>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>42</v>
+      </c>
+      <c r="B113" t="s">
         <v>50</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D102" t="s">
-        <v>81</v>
-      </c>
-      <c r="E102">
-        <v>71</v>
-      </c>
-      <c r="F102">
-        <v>2080</v>
-      </c>
-      <c r="G102">
-        <v>7</v>
-      </c>
-      <c r="H102">
-        <v>0</v>
-      </c>
-      <c r="I102" s="2"/>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>30</v>
-      </c>
-      <c r="B103" t="s">
+      <c r="C113" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113">
+        <v>122</v>
+      </c>
+      <c r="F113">
+        <v>6670</v>
+      </c>
+      <c r="G113">
+        <v>10</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113" s="2"/>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>43</v>
+      </c>
+      <c r="B114" t="s">
         <v>51</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D103" t="s">
-        <v>81</v>
-      </c>
-      <c r="E103">
-        <v>120</v>
-      </c>
-      <c r="F103">
-        <v>6441</v>
-      </c>
-      <c r="G103">
-        <v>9</v>
-      </c>
-      <c r="H103">
-        <v>0</v>
-      </c>
-      <c r="I103" s="2"/>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <v>31</v>
-      </c>
-      <c r="B104" t="s">
+      <c r="C114" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114">
+        <v>118</v>
+      </c>
+      <c r="F114">
+        <v>6216</v>
+      </c>
+      <c r="G114">
+        <v>4</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114" s="2"/>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>44</v>
+      </c>
+      <c r="B115" t="s">
         <v>52</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D104" t="s">
-        <v>81</v>
-      </c>
-      <c r="E104">
-        <v>126</v>
-      </c>
-      <c r="F104">
-        <v>7140</v>
-      </c>
-      <c r="G104">
-        <v>10</v>
-      </c>
-      <c r="H104">
-        <v>0</v>
-      </c>
-      <c r="I104" s="2">
-        <f>AVERAGE(E104:E108)</f>
-        <v>241.8</v>
-      </c>
-      <c r="J104">
-        <f>MAX(E104:E108)</f>
-        <v>735</v>
-      </c>
-      <c r="K104" s="2">
-        <f>AVERAGE(F104:F108)</f>
-        <v>54101.2</v>
-      </c>
-      <c r="L104">
-        <f>MAX(F104:F108)</f>
-        <v>245350</v>
-      </c>
-      <c r="M104" s="2">
-        <f>AVERAGE(G104:G108)</f>
-        <v>10</v>
-      </c>
-      <c r="N104">
-        <f>MAX(G104:G108)</f>
-        <v>10</v>
-      </c>
-      <c r="O104" s="2">
-        <f>AVERAGE(H104:H108)</f>
-        <v>58.4</v>
-      </c>
-      <c r="P104">
-        <f>MAX(H104:H108)</f>
-        <v>292</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <v>32</v>
-      </c>
-      <c r="B105" t="s">
+      <c r="C115" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115">
+        <v>153</v>
+      </c>
+      <c r="F115">
+        <v>10731</v>
+      </c>
+      <c r="G115">
+        <v>10</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115" s="2"/>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>45</v>
+      </c>
+      <c r="B116" t="s">
         <v>53</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D105" t="s">
-        <v>81</v>
-      </c>
-      <c r="E105">
-        <v>111</v>
-      </c>
-      <c r="F105">
-        <v>5460</v>
-      </c>
-      <c r="G105">
-        <v>10</v>
-      </c>
-      <c r="H105">
-        <v>0</v>
-      </c>
-      <c r="I105" s="2"/>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <v>33</v>
-      </c>
-      <c r="B106" t="s">
+      <c r="C116" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116">
+        <v>737</v>
+      </c>
+      <c r="F116">
+        <v>246753</v>
+      </c>
+      <c r="G116">
+        <v>10</v>
+      </c>
+      <c r="H116">
+        <v>310</v>
+      </c>
+      <c r="I116" s="2"/>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>46</v>
+      </c>
+      <c r="B117" t="s">
         <v>54</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D106" t="s">
-        <v>81</v>
-      </c>
-      <c r="E106">
-        <v>115</v>
-      </c>
-      <c r="F106">
-        <v>5886</v>
-      </c>
-      <c r="G106">
-        <v>10</v>
-      </c>
-      <c r="H106">
-        <v>0</v>
-      </c>
-      <c r="I106" s="2"/>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <v>34</v>
-      </c>
-      <c r="B107" t="s">
-        <v>55</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D107" t="s">
-        <v>81</v>
-      </c>
-      <c r="E107">
-        <v>122</v>
-      </c>
-      <c r="F107">
-        <v>6670</v>
-      </c>
-      <c r="G107">
-        <v>10</v>
-      </c>
-      <c r="H107">
-        <v>0</v>
-      </c>
-      <c r="I107" s="2"/>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A108">
-        <v>35</v>
-      </c>
-      <c r="B108" t="s">
-        <v>56</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D108" t="s">
-        <v>81</v>
-      </c>
-      <c r="E108">
-        <v>735</v>
-      </c>
-      <c r="F108">
-        <v>245350</v>
-      </c>
-      <c r="G108">
-        <v>10</v>
-      </c>
-      <c r="H108">
-        <v>292</v>
-      </c>
-      <c r="I108" s="2"/>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A109">
-        <v>36</v>
-      </c>
-      <c r="B109" t="s">
-        <v>57</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D109" t="s">
-        <v>81</v>
-      </c>
-      <c r="E109">
-        <v>136</v>
-      </c>
-      <c r="F109">
-        <v>8385</v>
-      </c>
-      <c r="G109">
-        <v>10</v>
-      </c>
-      <c r="H109">
-        <v>1</v>
-      </c>
-      <c r="I109" s="2">
-        <f>AVERAGE(E109:E113)</f>
-        <v>246</v>
-      </c>
-      <c r="J109">
-        <f>MAX(E109:E113)</f>
-        <v>738</v>
-      </c>
-      <c r="K109" s="2">
-        <f>AVERAGE(F109:F113)</f>
-        <v>54945.4</v>
-      </c>
-      <c r="L109">
-        <f>MAX(F109:F113)</f>
-        <v>247456</v>
-      </c>
-      <c r="M109" s="2">
-        <f>AVERAGE(G109:G113)</f>
-        <v>10</v>
-      </c>
-      <c r="N109">
-        <f>MAX(G109:G113)</f>
-        <v>10</v>
-      </c>
-      <c r="O109" s="2">
-        <f>AVERAGE(H109:H113)</f>
-        <v>65.2</v>
-      </c>
-      <c r="P109">
-        <f>MAX(H109:H113)</f>
-        <v>325</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A110">
-        <v>37</v>
-      </c>
-      <c r="B110" t="s">
-        <v>58</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D110" t="s">
-        <v>81</v>
-      </c>
-      <c r="E110">
-        <v>116</v>
-      </c>
-      <c r="F110">
-        <v>5995</v>
-      </c>
-      <c r="G110">
-        <v>10</v>
-      </c>
-      <c r="H110">
-        <v>0</v>
-      </c>
-      <c r="I110" s="2"/>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A111">
-        <v>38</v>
-      </c>
-      <c r="B111" t="s">
-        <v>59</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D111" t="s">
-        <v>81</v>
-      </c>
-      <c r="E111">
-        <v>123</v>
-      </c>
-      <c r="F111">
-        <v>6786</v>
-      </c>
-      <c r="G111">
-        <v>10</v>
-      </c>
-      <c r="H111">
-        <v>0</v>
-      </c>
-      <c r="I111" s="2"/>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A112">
-        <v>39</v>
-      </c>
-      <c r="B112" t="s">
-        <v>60</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D112" t="s">
-        <v>81</v>
-      </c>
-      <c r="E112">
-        <v>117</v>
-      </c>
-      <c r="F112">
-        <v>6105</v>
-      </c>
-      <c r="G112">
-        <v>10</v>
-      </c>
-      <c r="H112">
-        <v>0</v>
-      </c>
-      <c r="I112" s="2"/>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A113">
-        <v>40</v>
-      </c>
-      <c r="B113" t="s">
-        <v>1</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D113" t="s">
-        <v>81</v>
-      </c>
-      <c r="E113">
-        <v>738</v>
-      </c>
-      <c r="F113">
-        <v>247456</v>
-      </c>
-      <c r="G113">
-        <v>10</v>
-      </c>
-      <c r="H113">
-        <v>325</v>
-      </c>
-      <c r="I113" s="2"/>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A114">
-        <v>41</v>
-      </c>
-      <c r="B114" t="s">
-        <v>61</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D114" t="s">
-        <v>81</v>
-      </c>
-      <c r="E114">
-        <v>162</v>
-      </c>
-      <c r="F114">
-        <v>12090</v>
-      </c>
-      <c r="G114">
-        <v>10</v>
-      </c>
-      <c r="H114">
-        <v>1</v>
-      </c>
-      <c r="I114" s="2">
-        <f>AVERAGE(E114:E118)</f>
-        <v>258.39999999999998</v>
-      </c>
-      <c r="J114">
-        <f>MAX(E114:E118)</f>
-        <v>737</v>
-      </c>
-      <c r="K114" s="2">
-        <f>AVERAGE(F114:F118)</f>
-        <v>56492</v>
-      </c>
-      <c r="L114">
-        <f>MAX(F114:F118)</f>
-        <v>246753</v>
-      </c>
-      <c r="M114" s="2">
-        <f>AVERAGE(G114:G118)</f>
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="N114">
-        <f>MAX(G114:G118)</f>
-        <v>10</v>
-      </c>
-      <c r="O114" s="2">
-        <f>AVERAGE(H114:H118)</f>
-        <v>62.4</v>
-      </c>
-      <c r="P114">
-        <f>MAX(H114:H118)</f>
-        <v>310</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A115">
-        <v>42</v>
-      </c>
-      <c r="B115" t="s">
-        <v>62</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D115" t="s">
-        <v>81</v>
-      </c>
-      <c r="E115">
-        <v>122</v>
-      </c>
-      <c r="F115">
-        <v>6670</v>
-      </c>
-      <c r="G115">
-        <v>10</v>
-      </c>
-      <c r="H115">
-        <v>0</v>
-      </c>
-      <c r="I115" s="2"/>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A116">
-        <v>43</v>
-      </c>
-      <c r="B116" t="s">
-        <v>63</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D116" t="s">
-        <v>81</v>
-      </c>
-      <c r="E116">
-        <v>118</v>
-      </c>
-      <c r="F116">
-        <v>6216</v>
-      </c>
-      <c r="G116">
-        <v>4</v>
-      </c>
-      <c r="H116">
-        <v>0</v>
-      </c>
-      <c r="I116" s="2"/>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A117">
-        <v>44</v>
-      </c>
-      <c r="B117" t="s">
-        <v>64</v>
-      </c>
       <c r="C117" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D117" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E117">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="F117">
-        <v>10731</v>
+        <v>12403</v>
       </c>
       <c r="G117">
         <v>10</v>
@@ -4636,105 +4629,105 @@
       <c r="H117">
         <v>1</v>
       </c>
-      <c r="I117" s="2"/>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I117" s="2">
+        <f>AVERAGE(E117:E121)</f>
+        <v>280</v>
+      </c>
+      <c r="J117">
+        <f>MAX(E117:E121)</f>
+        <v>866</v>
+      </c>
+      <c r="K117" s="2">
+        <f>AVERAGE(F117:F121)</f>
+        <v>74559.8</v>
+      </c>
+      <c r="L117">
+        <f>MAX(F117:F121)</f>
+        <v>339900</v>
+      </c>
+      <c r="M117" s="2">
+        <f>AVERAGE(G117:G121)</f>
+        <v>10</v>
+      </c>
+      <c r="N117">
+        <f>MAX(G117:G121)</f>
+        <v>10</v>
+      </c>
+      <c r="O117" s="2">
+        <f>AVERAGE(H117:H121)</f>
+        <v>105.8</v>
+      </c>
+      <c r="P117">
+        <f>MAX(H117:H121)</f>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B118" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D118" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E118">
-        <v>737</v>
+        <v>126</v>
       </c>
       <c r="F118">
-        <v>246753</v>
+        <v>7140</v>
       </c>
       <c r="G118">
         <v>10</v>
       </c>
       <c r="H118">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="I118" s="2"/>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B119" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D119" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E119">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="F119">
-        <v>12403</v>
+        <v>6216</v>
       </c>
       <c r="G119">
         <v>10</v>
       </c>
       <c r="H119">
-        <v>1</v>
-      </c>
-      <c r="I119" s="2">
-        <f>AVERAGE(E119:E123)</f>
-        <v>280</v>
-      </c>
-      <c r="J119">
-        <f>MAX(E119:E123)</f>
-        <v>866</v>
-      </c>
-      <c r="K119" s="2">
-        <f>AVERAGE(F119:F123)</f>
-        <v>74559.8</v>
-      </c>
-      <c r="L119">
-        <f>MAX(F119:F123)</f>
-        <v>339900</v>
-      </c>
-      <c r="M119" s="2">
-        <f>AVERAGE(G119:G123)</f>
-        <v>10</v>
-      </c>
-      <c r="N119">
-        <f>MAX(G119:G123)</f>
-        <v>10</v>
-      </c>
-      <c r="O119" s="2">
-        <f>AVERAGE(H119:H123)</f>
-        <v>105.8</v>
-      </c>
-      <c r="P119">
-        <f>MAX(H119:H123)</f>
-        <v>528</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="I119" s="2"/>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B120" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D120" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E120">
         <v>126</v>
@@ -4750,51 +4743,51 @@
       </c>
       <c r="I120" s="2"/>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B121" t="s">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D121" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E121">
-        <v>118</v>
+        <v>866</v>
       </c>
       <c r="F121">
-        <v>6216</v>
+        <v>339900</v>
       </c>
       <c r="G121">
         <v>10</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="I121" s="2"/>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B122" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D122" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E122">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F122">
-        <v>7140</v>
+        <v>5253</v>
       </c>
       <c r="G122">
         <v>10</v>
@@ -4802,53 +4795,84 @@
       <c r="H122">
         <v>0</v>
       </c>
-      <c r="I122" s="2"/>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I122" s="2">
+        <f>AVERAGE(E122:E126)</f>
+        <v>232.8</v>
+      </c>
+      <c r="J122">
+        <f>MAX(E122:E126)</f>
+        <v>737</v>
+      </c>
+      <c r="K122" s="2">
+        <f>AVERAGE(F122:F126)</f>
+        <v>53371.199999999997</v>
+      </c>
+      <c r="L122">
+        <f>MAX(F122:F126)</f>
+        <v>246753</v>
+      </c>
+      <c r="M122" s="2">
+        <f>AVERAGE(G122:G126)</f>
+        <v>10</v>
+      </c>
+      <c r="N122">
+        <f>MAX(G122:G126)</f>
+        <v>10</v>
+      </c>
+      <c r="O122" s="2">
+        <f>AVERAGE(H122:H126)</f>
+        <v>60.4</v>
+      </c>
+      <c r="P122">
+        <f>MAX(H122:H126)</f>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B123" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D123" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E123">
-        <v>866</v>
+        <v>106</v>
       </c>
       <c r="F123">
-        <v>339900</v>
+        <v>4950</v>
       </c>
       <c r="G123">
         <v>10</v>
       </c>
       <c r="H123">
-        <v>528</v>
+        <v>0</v>
       </c>
       <c r="I123" s="2"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B124" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D124" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E124">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F124">
-        <v>5253</v>
+        <v>4950</v>
       </c>
       <c r="G124">
         <v>10</v>
@@ -4856,51 +4880,20 @@
       <c r="H124">
         <v>0</v>
       </c>
-      <c r="I124" s="2">
-        <f>AVERAGE(E124:E128)</f>
-        <v>232.8</v>
-      </c>
-      <c r="J124">
-        <f>MAX(E124:E128)</f>
-        <v>737</v>
-      </c>
-      <c r="K124" s="2">
-        <f>AVERAGE(F124:F128)</f>
-        <v>53371.199999999997</v>
-      </c>
-      <c r="L124">
-        <f>MAX(F124:F128)</f>
-        <v>246753</v>
-      </c>
-      <c r="M124" s="2">
-        <f>AVERAGE(G124:G128)</f>
-        <v>10</v>
-      </c>
-      <c r="N124">
-        <f>MAX(G124:G128)</f>
-        <v>10</v>
-      </c>
-      <c r="O124" s="2">
-        <f>AVERAGE(H124:H128)</f>
-        <v>60.4</v>
-      </c>
-      <c r="P124">
-        <f>MAX(H124:H128)</f>
-        <v>302</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I124" s="2"/>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B125" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D125" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E125">
         <v>106</v>
@@ -4916,325 +4909,327 @@
       </c>
       <c r="I125" s="2"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B126" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D126" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E126">
-        <v>106</v>
+        <v>737</v>
       </c>
       <c r="F126">
-        <v>4950</v>
+        <v>246753</v>
       </c>
       <c r="G126">
         <v>10</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="I126" s="2"/>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B127" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="D127" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E127">
-        <v>106</v>
+        <v>180</v>
       </c>
       <c r="F127">
-        <v>4950</v>
+        <v>14878</v>
       </c>
       <c r="G127">
         <v>10</v>
       </c>
       <c r="H127">
-        <v>0</v>
-      </c>
-      <c r="I127" s="2"/>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="I127" s="2">
+        <f>AVERAGE(E127:E131)</f>
+        <v>260.39999999999998</v>
+      </c>
+      <c r="J127">
+        <f>MAX(E127:E131)</f>
+        <v>701</v>
+      </c>
+      <c r="K127" s="2">
+        <f>AVERAGE(F127:F131)</f>
+        <v>53106.2</v>
+      </c>
+      <c r="L127">
+        <f>MAX(F127:F131)</f>
+        <v>222778</v>
+      </c>
+      <c r="M127" s="2">
+        <f>AVERAGE(G127:G131)</f>
+        <v>10</v>
+      </c>
+      <c r="N127">
+        <f>MAX(G127:G131)</f>
+        <v>10</v>
+      </c>
+      <c r="O127" s="2">
+        <f>AVERAGE(H127:H131)</f>
+        <v>57.8</v>
+      </c>
+      <c r="P127">
+        <f>MAX(H127:H131)</f>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B128" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="D128" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E128">
-        <v>737</v>
+        <v>177</v>
       </c>
       <c r="F128">
-        <v>246753</v>
+        <v>14535</v>
       </c>
       <c r="G128">
         <v>10</v>
       </c>
       <c r="H128">
-        <v>302</v>
+        <v>2</v>
       </c>
       <c r="I128" s="2"/>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B129" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D129" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E129">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="F129">
-        <v>14878</v>
+        <v>6670</v>
       </c>
       <c r="G129">
         <v>10</v>
       </c>
       <c r="H129">
-        <v>2</v>
-      </c>
-      <c r="I129" s="2">
-        <f>AVERAGE(E129:E133)</f>
-        <v>260.39999999999998</v>
-      </c>
-      <c r="J129">
-        <f>MAX(E129:E133)</f>
+        <v>0</v>
+      </c>
+      <c r="I129" s="2"/>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>59</v>
+      </c>
+      <c r="B130" t="s">
+        <v>66</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130">
+        <v>122</v>
+      </c>
+      <c r="F130">
+        <v>6670</v>
+      </c>
+      <c r="G130">
+        <v>10</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130" s="2"/>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>60</v>
+      </c>
+      <c r="B131" t="s">
+        <v>67</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131">
         <v>701</v>
       </c>
-      <c r="K129" s="2">
-        <f>AVERAGE(F129:F133)</f>
-        <v>53106.2</v>
-      </c>
-      <c r="L129">
-        <f>MAX(F129:F133)</f>
+      <c r="F131">
         <v>222778</v>
       </c>
-      <c r="M129" s="2">
-        <f>AVERAGE(G129:G133)</f>
-        <v>10</v>
-      </c>
-      <c r="N129">
-        <f>MAX(G129:G133)</f>
-        <v>10</v>
-      </c>
-      <c r="O129" s="2">
-        <f>AVERAGE(H129:H133)</f>
-        <v>57.8</v>
-      </c>
-      <c r="P129">
-        <f>MAX(H129:H133)</f>
+      <c r="G131">
+        <v>10</v>
+      </c>
+      <c r="H131">
         <v>285</v>
       </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A130">
-        <v>57</v>
-      </c>
-      <c r="B130" t="s">
-        <v>76</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D130" t="s">
-        <v>81</v>
-      </c>
-      <c r="E130">
-        <v>177</v>
-      </c>
-      <c r="F130">
-        <v>14535</v>
-      </c>
-      <c r="G130">
-        <v>10</v>
-      </c>
-      <c r="H130">
-        <v>2</v>
-      </c>
-      <c r="I130" s="2"/>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A131">
-        <v>58</v>
-      </c>
-      <c r="B131" t="s">
-        <v>77</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D131" t="s">
-        <v>81</v>
-      </c>
-      <c r="E131">
-        <v>122</v>
-      </c>
-      <c r="F131">
-        <v>6670</v>
-      </c>
-      <c r="G131">
-        <v>10</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
       <c r="I131" s="2"/>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>59</v>
+        <f>1+A131</f>
+        <v>61</v>
       </c>
       <c r="B132" t="s">
-        <v>78</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
+      </c>
+      <c r="C132" t="s">
+        <v>104</v>
       </c>
       <c r="D132" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E132">
-        <v>122</v>
+        <v>253</v>
       </c>
       <c r="F132">
-        <v>6670</v>
+        <v>29403</v>
       </c>
       <c r="G132">
         <v>10</v>
       </c>
       <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132" s="2"/>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="I132" s="2">
+        <f>AVERAGE(E132:E143)</f>
+        <v>257.8</v>
+      </c>
+      <c r="J132">
+        <f>MAX(E132:E143)</f>
+        <v>265</v>
+      </c>
+      <c r="K132" s="2">
+        <f>AVERAGE(F132:F143)</f>
+        <v>30394.2</v>
+      </c>
+      <c r="L132">
+        <f>MAX(F132:F143)</f>
+        <v>32131</v>
+      </c>
+      <c r="M132" s="2">
+        <f>AVERAGE(G132:G143)</f>
+        <v>10</v>
+      </c>
+      <c r="N132">
+        <f>MAX(G132:G143)</f>
+        <v>10</v>
+      </c>
+      <c r="O132" s="2">
+        <f>AVERAGE(H132:H143)</f>
+        <v>5.9</v>
+      </c>
+      <c r="P132">
+        <f>MAX(H132:H143)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>60</v>
+        <f t="shared" ref="A133:A143" si="1">1+A132</f>
+        <v>62</v>
       </c>
       <c r="B133" t="s">
-        <v>79</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
+      </c>
+      <c r="C133" t="s">
+        <v>104</v>
       </c>
       <c r="D133" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E133">
-        <v>701</v>
+        <v>265</v>
       </c>
       <c r="F133">
-        <v>222778</v>
+        <v>32131</v>
       </c>
       <c r="G133">
         <v>10</v>
       </c>
       <c r="H133">
-        <v>285</v>
+        <v>6</v>
       </c>
       <c r="I133" s="2"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134">
-        <f>1+A133</f>
-        <v>61</v>
+        <f t="shared" si="1"/>
+        <v>63</v>
       </c>
       <c r="B134" t="s">
-        <v>4</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>19</v>
+        <v>96</v>
+      </c>
+      <c r="C134" t="s">
+        <v>104</v>
       </c>
       <c r="D134" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E134">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="F134">
-        <v>29403</v>
+        <v>32131</v>
       </c>
       <c r="G134">
         <v>10</v>
       </c>
       <c r="H134">
-        <v>5</v>
-      </c>
-      <c r="I134" s="2">
-        <f>AVERAGE(E134:E145)</f>
-        <v>265</v>
-      </c>
-      <c r="J134">
-        <f>MAX(E134:E145)</f>
-        <v>367</v>
-      </c>
-      <c r="K134" s="2">
-        <f>AVERAGE(F134:F145)</f>
-        <v>32627.083333333332</v>
-      </c>
-      <c r="L134">
-        <f>MAX(F134:F145)</f>
-        <v>61423</v>
-      </c>
-      <c r="M134" s="2">
-        <f>AVERAGE(G134:G145)</f>
-        <v>9.3333333333333339</v>
-      </c>
-      <c r="N134">
-        <f>MAX(G134:G145)</f>
-        <v>10</v>
-      </c>
-      <c r="O134" s="2">
-        <f>AVERAGE(H134:H145)</f>
-        <v>7.666666666666667</v>
-      </c>
-      <c r="P134">
-        <f>MAX(H134:H145)</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="I134" s="2"/>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135">
-        <f t="shared" ref="A135:A145" si="1">1+A134</f>
-        <v>62</v>
+        <f t="shared" si="1"/>
+        <v>64</v>
       </c>
       <c r="B135" t="s">
-        <v>8</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>19</v>
+        <v>97</v>
+      </c>
+      <c r="C135" t="s">
+        <v>104</v>
       </c>
       <c r="D135" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E135">
         <v>253</v>
@@ -5246,23 +5241,23 @@
         <v>10</v>
       </c>
       <c r="H135">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I135" s="2"/>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136">
         <f t="shared" si="1"/>
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B136" t="s">
-        <v>9</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>19</v>
+        <v>98</v>
+      </c>
+      <c r="C136" t="s">
+        <v>104</v>
       </c>
       <c r="D136" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E136">
         <v>253</v>
@@ -5278,19 +5273,19 @@
       </c>
       <c r="I136" s="2"/>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137">
         <f t="shared" si="1"/>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B137" t="s">
-        <v>10</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>19</v>
+        <v>99</v>
+      </c>
+      <c r="C137" t="s">
+        <v>105</v>
       </c>
       <c r="D137" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E137">
         <v>253</v>
@@ -5302,23 +5297,23 @@
         <v>10</v>
       </c>
       <c r="H137">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I137" s="2"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B138" t="s">
-        <v>11</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>19</v>
+        <v>100</v>
+      </c>
+      <c r="C138" t="s">
+        <v>105</v>
       </c>
       <c r="D138" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E138">
         <v>253</v>
@@ -5330,23 +5325,23 @@
         <v>10</v>
       </c>
       <c r="H138">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I138" s="2"/>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139">
         <f t="shared" si="1"/>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B139" t="s">
-        <v>12</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>19</v>
+        <v>101</v>
+      </c>
+      <c r="C139" t="s">
+        <v>105</v>
       </c>
       <c r="D139" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E139">
         <v>253</v>
@@ -5362,173 +5357,69 @@
       </c>
       <c r="I139" s="2"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140">
         <f t="shared" si="1"/>
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>19</v>
+        <v>102</v>
+      </c>
+      <c r="C140" t="s">
+        <v>105</v>
       </c>
       <c r="D140" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E140">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="F140">
-        <v>29403</v>
+        <v>32131</v>
       </c>
       <c r="G140">
         <v>10</v>
       </c>
       <c r="H140">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I140" s="2"/>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141">
         <f t="shared" si="1"/>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B141" t="s">
-        <v>14</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>19</v>
+        <v>103</v>
+      </c>
+      <c r="C141" t="s">
+        <v>105</v>
       </c>
       <c r="D141" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E141">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="F141">
-        <v>29403</v>
+        <v>31131</v>
       </c>
       <c r="G141">
         <v>10</v>
       </c>
       <c r="H141">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I141" s="2"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A142">
-        <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-      <c r="B142" t="s">
-        <v>5</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D142" t="s">
-        <v>81</v>
-      </c>
-      <c r="E142">
-        <v>367</v>
-      </c>
-      <c r="F142">
-        <v>61423</v>
-      </c>
-      <c r="G142">
-        <v>2</v>
-      </c>
-      <c r="H142">
-        <v>26</v>
-      </c>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C142" s="2"/>
       <c r="I142" s="2"/>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A143">
-        <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="B143" t="s">
-        <v>6</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D143" t="s">
-        <v>81</v>
-      </c>
-      <c r="E143">
-        <v>263</v>
-      </c>
-      <c r="F143">
-        <v>31626</v>
-      </c>
-      <c r="G143">
-        <v>10</v>
-      </c>
-      <c r="H143">
-        <v>8</v>
-      </c>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C143" s="2"/>
       <c r="I143" s="2"/>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A144">
-        <f t="shared" si="1"/>
-        <v>71</v>
-      </c>
-      <c r="B144" t="s">
-        <v>7</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D144" t="s">
-        <v>81</v>
-      </c>
-      <c r="E144">
-        <v>263</v>
-      </c>
-      <c r="F144">
-        <v>31626</v>
-      </c>
-      <c r="G144">
-        <v>10</v>
-      </c>
-      <c r="H144">
-        <v>7</v>
-      </c>
-      <c r="I144" s="2"/>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A145">
-        <f t="shared" si="1"/>
-        <v>72</v>
-      </c>
-      <c r="B145" t="s">
-        <v>15</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D145" t="s">
-        <v>81</v>
-      </c>
-      <c r="E145">
-        <v>263</v>
-      </c>
-      <c r="F145">
-        <v>31626</v>
-      </c>
-      <c r="G145">
-        <v>10</v>
-      </c>
-      <c r="H145">
-        <v>6</v>
-      </c>
-      <c r="I145" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5539,52 +5430,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12E6F7F7-EAF3-46EE-ADC1-A20EF71422C6}">
   <dimension ref="A1:K1048576"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G1" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="H1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="I1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="J1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="K1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D2">
         <v>122.6</v>
@@ -5611,15 +5502,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D3">
         <v>124.8</v>
@@ -5646,15 +5537,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D4">
         <v>139</v>
@@ -5681,15 +5572,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D5">
         <v>128</v>
@@ -5716,15 +5607,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D6">
         <v>91.8</v>
@@ -5751,15 +5642,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D7">
         <v>80.8</v>
@@ -5786,15 +5677,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>241.8</v>
@@ -5821,15 +5712,15 @@
         <v>288</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D9">
         <v>246</v>
@@ -5856,15 +5747,15 @@
         <v>308</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D10">
         <v>258.39999999999998</v>
@@ -5891,15 +5782,15 @@
         <v>298</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D11">
         <v>280</v>
@@ -5926,15 +5817,15 @@
         <v>532</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D12">
         <v>232.8</v>
@@ -5961,15 +5852,15 @@
         <v>292</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D13">
         <v>260.39999999999998</v>
@@ -5996,50 +5887,50 @@
         <v>286</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D14">
+        <v>257.8</v>
+      </c>
+      <c r="E14">
         <v>265</v>
       </c>
-      <c r="E14">
-        <v>367</v>
-      </c>
       <c r="F14" s="3">
-        <v>32627.083333333332</v>
+        <v>30394.2</v>
       </c>
       <c r="G14">
-        <v>61423</v>
+        <v>32131</v>
       </c>
       <c r="H14" s="3">
-        <v>3.0833333333333335</v>
+        <v>4.2</v>
       </c>
       <c r="I14">
         <v>7</v>
       </c>
       <c r="J14" s="3">
-        <v>7.583333333333333</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D15">
         <v>122.6</v>
@@ -6066,15 +5957,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D16">
         <v>124.8</v>
@@ -6101,15 +5992,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D17">
         <v>139</v>
@@ -6136,15 +6027,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D18">
         <v>128</v>
@@ -6171,15 +6062,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D19">
         <v>91.8</v>
@@ -6206,15 +6097,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D20">
         <v>80.8</v>
@@ -6241,15 +6132,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D21">
         <v>241.8</v>
@@ -6276,15 +6167,15 @@
         <v>292</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D22">
         <v>246</v>
@@ -6311,15 +6202,15 @@
         <v>325</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D23">
         <v>258.39999999999998</v>
@@ -6346,15 +6237,15 @@
         <v>310</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D24">
         <v>280</v>
@@ -6381,15 +6272,15 @@
         <v>528</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D25">
         <v>232.8</v>
@@ -6416,15 +6307,15 @@
         <v>302</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D26">
         <v>260.39999999999998</v>
@@ -6451,42 +6342,42 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D27">
+        <v>257.8</v>
+      </c>
+      <c r="E27">
         <v>265</v>
       </c>
-      <c r="E27">
-        <v>367</v>
-      </c>
       <c r="F27" s="3">
-        <v>32627.083333333332</v>
+        <v>30394.2</v>
       </c>
       <c r="G27">
-        <v>61423</v>
+        <v>32131</v>
       </c>
       <c r="H27" s="3">
-        <v>9.3333333333333339</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>10</v>
       </c>
       <c r="J27" s="3">
-        <v>7.666666666666667</v>
+        <v>5.9</v>
       </c>
       <c r="K27">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="1048576" spans="1:1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1048576" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1048576" t="s">
         <v>3</v>
       </c>
